--- a/Problem12_360_Customer_Intelligence/reports/financial_impact_reporting_packaging/AMEX_Problem12_Financial_Impact_Workbook.xlsx
+++ b/Problem12_360_Customer_Intelligence/reports/financial_impact_reporting_packaging/AMEX_Problem12_Financial_Impact_Workbook.xlsx
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -139,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,7 +156,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,13 +171,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -720,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -730,6 +743,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -744,6 +758,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -774,7 +795,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="20">
         <f>'Efficiency Impact'!B10</f>
         <v/>
       </c>
@@ -902,7 +923,7 @@
           <t>Minutes Saved Per Case Lookup</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="21" t="n">
         <v>6</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -917,7 +938,7 @@
           <t>Fully Loaded Hourly Labor Cost Usd</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="22" t="n">
         <v>42</v>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -932,7 +953,7 @@
           <t>Ongoing Hosting Cost Usd Per Cycle</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="22" t="n">
         <v>350</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -947,7 +968,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="22" t="n">
         <v>45000</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1070,7 +1091,7 @@
           <t>Gross Productivity Savings / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="23">
         <f>B3*(Assumptions!$B$3/60)*Assumptions!$B$4</f>
         <v/>
       </c>
@@ -1081,7 +1102,7 @@
           <t>Ongoing Hosting Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="23">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1092,7 +1113,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="23">
         <f>B8-B9</f>
         <v/>
       </c>
@@ -1103,7 +1124,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="23">
         <f>B10*Assumptions!$B$7</f>
         <v/>
       </c>
